--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), il reste environ 9 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +51 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +51 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), il reste environ 9 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), il reste environ 9 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), il reste environ 24 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Restauration légère possible (sans conduit)</t>
+          <t>Extraction / vraie restauration possible · Restauration légère possible (sans conduit) · Activités restreintes · Terrasse</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Restauration sans conduit possible</t>
+          <t>190 000 € 4 524 €/m² MURS - LOCAL COMMERCIAL - RUE BOULARD 75014 42 m² Mouton Duvernet, Paris 14ème arrondissement (75014) Voir l'annonce</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), il reste environ 24 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 38 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-14e-31e99507.xlsx
+++ b/docs/dossiers/dossier-paris-14e-31e99507.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
